--- a/medford_videoprotsessory_dlya_zhestkoy_endoskopii.xlsx
+++ b/medford_videoprotsessory_dlya_zhestkoy_endoskopii.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры для жесткой эндоскопии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Mindray, MGB — всего 15 позиций.</t>
+          <t>Видеопроцессоры для жесткой эндоскопии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Mindray, MGB.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_videoprotsessory_dlya_zhestkoy_endoskopii.xlsx
+++ b/medford_videoprotsessory_dlya_zhestkoy_endoskopii.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать видеопроцессоры для жесткой эндоскопии для клиники?</t>
+          <t>Что такое видеопроцессор для жёсткой эндоскопии?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Производитель, Страна производства, Вес головки камеры, г, Разрешение, пикселей). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Это блок обработки видеосигнала в связке с эндоскопической камерой, который формирует и выводит изображение с жёсткого эндоскопа на монитор. Он отвечает за качество, цветопередачу и обработку картинки в ходе эндовидеохирургии. В каталоге есть отдельные блоки и интегрированные системы с источником света.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какое разрешение выбрать: Full HD или 4K?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Full HD (1920×1080) достаточно для большинства рутинных вмешательств. 4K UHD (3840×2160) даёт больше детализации и оправдан в сложной хирургии и на крупных мониторах. Для 4K нужен совместимый монитор. В каталоге есть обе категории — Mindray HD3 (Full HD) и HyPixel U1, Olympus Visera 4K UHD.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Чем интегрированная система отличается от отдельного блока?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Olympus, Mindray, MGB. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Отдельный блок управления камерой работает в связке со стойкой и источником света, узлы можно менять по отдельности. Интегрированная система (MGB ELICA III, Fencer III «4 в 1») объединяет камеру, свет, иногда инсуффлятор и ирригатор в одном корпусе — это компактно и удобно, но менее гибко при модернизации.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Одночиповая или трёхчиповая камера?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Одночиповые камеры компактнее и дешевле, их разрешения достаточно для многих задач. Трёхчиповые дают более точную цветопередачу за счёт раздельной обработки цветов. Выбор зависит от требований к качеству изображения и бюджета. В каталоге есть одночиповые Full HD-камеры MGB.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Совместим ли видеопроцессор с моими эндоскопами и монитором?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Камера стыкуется с жёстким эндоскопом через адаптер-окуляр, а процессор — с монитором по видеовыходу. Совместимость зависит от типа крепления и разъёмов. Сообщите, какие эндоскопы и монитор используете, и мы сверим подключение; для 4K потребуется совместимый 4K-монитор.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Почему важен вес головки камеры?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Головкой камеры хирург манипулирует руками в ходе операции, поэтому её вес влияет на усталость при длительных вмешательствах. В каталоге вес головки указан от 235 г (Mindray HD3) до 420 г (MGB ARISTO-V3). Более лёгкая головка удобнее, но вес стоит соотносить с функциональностью модели.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>videoprotsessory_dlya_zhestkoy_endoskopii</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли РУ и есть ли сервис?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Видеопроцессор для эндоскопии — медицинское изделие, для применения нужно действующее РУ Росздравнадзора. На поставляемые системы распространяется гарантия, обслуживание и ремонт камер и блоков выполняет собственный инженерный сервис. Реквизиты РУ и условия по модели уточняйте у менеджера.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>videoprotsessory_dlya_zhestkoy_endoskopii</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры для жесткой эндоскопии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Mindray, MGB.</t>
+          <t>Видеопроцессоры для жёсткой эндоскопии — это блоки обработки сигнала с эндоскопической камерой, формирующие изображение с жёсткого эндоскопа на монитор. В каталоге представлены видеоинформационные центры Olympus (Visera Elite, Elite II, 4K UHD), блоки управления камерой Mindray (HD3 с разрешением 1920×1080, HyPixel U1 с 4K 3840×2160), интегрированные системы MGB (ELICA III, Fencer III «4 в 1») и отечественные камеры НПФ Крыло и «Элепс». Разрешение варьируется от HD до 4K UHD.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Видеосистемы для жёсткой эндоскопии по разрешению</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое видеопроцессоры для жесткой эндоскопии</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3985,239 +4061,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Видеосистемы для жёсткой эндоскопии по разрешению</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Класс</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Разрешение</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Архитектура</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Вес головки камеры, г</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Разрешение, пикселей</t>
+          <t>Пример моделей</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Видеоинформационный центр Olympus OTV-S200 (Visera Elite II)</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>1280×720</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>58577</t>
+          <t>Камера/блок</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Япония</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>НПФ Крыло КРВ 1001ОС, Chammed-класс</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Видеоинформационный центр Olympus OTV-S400 (Visera 4K UHD)</t>
+          <t>Full HD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>1920×1080</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>58577</t>
+          <t>Блок или интегрированная</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Япония</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mindray HD3, НПФ Крыло КРВ 1001HD, MGB ARISTO-V1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Видеокамера эндоскопическая "Элепс" EVK-001</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>4K UHD</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>3840×2160</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Блок управления камерой</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Видеорекордер Крыло</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>67299</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Видеокамера эндоскопическая НПФ Крыло КРВ 1001HD с разрешением Full HD</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>67299</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Mindray HD3 (основной блок управления камерой + головка видеокамеры)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Mindray</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080</t>
+          <t>Mindray HyPixel U1, Olympus Visera 4K UHD</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4229,7 +4179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4555,12 +4505,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите нужное разрешение</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается видеопроцессоры для жесткой эндоскопии: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Разрешение задаёт детализацию картинки. HD (1280×720) и Full HD (1920×1080) закрывают рутинные задачи, 4K UHD (3840×2160) нужен для сложной хирургии и крупных мониторов. В каталоге есть Full HD (Mindray HD3, НПФ Крыло КРВ 1001HD) и 4K (Mindray HyPixel U1, Olympus Visera 4K UHD). Выбор — под задачи отделения.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4600,12 +4550,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите архитектуру: блок или интегрированная система</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Отдельный блок управления камерой (Mindray HD3, HyPixel U1) работает в связке с источником света и стойкой, его узлы меняют по отдельности. Интегрированные системы MGB ELICA III и Fencer III «4 в 1» объединяют камеру, свет, а иногда инсуффлятор и ирригатор — компактно, но менее гибко при апгрейде.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4645,12 +4595,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте число чипов матрицы</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Производитель, Страна производства, Вес головки камеры, г, Разрешение, пикселей. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Одночиповые камеры (CMOS/CCD) компактнее и дешевле, трёхчиповые дают более точную цветопередачу. В каталоге есть одночиповые Full HD (MGB ARISTO-V1, Chammed-класс) и системы разного уровня. Число чипов сопоставьте с требованиями к цвету и бюджетом отделения.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4690,12 +4640,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Сверьте совместимость с эндоскопами и монитором</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Olympus, Mindray, MGB.</t>
+          <t>Камера стыкуется с жёстким эндоскопом через адаптер-окуляр, а процессор — с монитором по видеовыходу. Уточните тип крепления камеры, поддерживаемые эндоскопы и разъёмы монитора. Для 4K нужен совместимый 4K-монитор, иначе преимущество разрешения не реализуется.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4735,12 +4685,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Оцените вес и эргономику головки камеры</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Головкой камеры хирург работает руками, поэтому её вес важен для длительных операций. В каталоге вес головки указан от 235 до 420 г (Mindray HD3 — 235 г, MGB ARISTO-V3 — 420 г). Более лёгкая головка снижает усталость; учитывайте баланс между весом и функциональностью.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4780,12 +4730,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните комплект, РУ и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Проверьте состав системы: блок, головка камеры, кабели, адаптеры, при необходимости источник света. Видеопроцессор — медицинское изделие, уточните действующее РУ Росздравнадзора. Обслуживание и ремонт выполняет инженерный сервис; условия гарантии по конкретной модели уточняйте у менеджера.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4835,7 +4785,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры для жесткой эндоскопии подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Olympus, Mindray, MGB. При выборе обращают внимание на производитель, страна производства, вес головки камеры, разрешение, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>В видеосистеме для жёсткой эндоскопии я отталкиваюсь от требуемого разрешения и совместимости. Для рутинных задач достаточно Full HD, для сложной хирургии берут 4K — например, Mindray HyPixel U1 или Olympus Visera 4K. Интегрированные системы «всё в одном» экономят место, но менее гибки при замене узлов. Обязательно проверяю стыковку камеры с имеющимися эндоскопами и монитором, а также вес головки камеры — с ним хирург работает руками.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5119,13 +5069,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое видеопроцессоры для жесткой эндоскопии</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры для жесткой эндоскопии — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Olympus, Mindray, MGB. Подберём вариант под задачи вашего отделения.</t>
+          <t>Видеопроцессор для жёсткой эндоскопии — блок обработки сигнала с эндоскопической камерой, который формирует изображение с жёсткого эндоскопа на монитор. Системы различаются разрешением — от HD (1280×720) и Full HD (1920×1080) до 4K UHD (3840×2160) — и числом чипов матрицы. Бывают отдельные блоки управления камерой и интегрированные системы, объединяющие камеру, источник света, инсуффлятор и ирригатор. При выборе смотрят на разрешение, совместимость с эндоскопами и монитором, а также вес головки камеры, которой хирург работает руками. Требуется действующее РУ Росздравнадзора.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5162,13 +5112,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое видеопроцессор для жёсткой эндоскопии</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Производитель, Страна производства, Вес головки камеры, г, Разрешение, пикселей), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Видеопроцессор для жёсткой эндоскопии — блок обработки видеосигнала, работающий с эндоскопической камерой и формирующий изображение с жёсткого эндоскопа на монитор. Он отвечает за качество, цветопередачу и обработку картинки при эндовидеохирургии. Вместе с источником света и монитором процессор образует эндоскопическую видеосистему операционной.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5205,13 +5155,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Разрешение и число чипов</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Системы различаются разрешением: HD (1280×720), Full HD (1920×1080) и 4K UHD (3840×2160). Чем выше разрешение, тем детальнее картинка, но для 4K нужен совместимый монитор. По матрице камеры бывают одночиповыми (компактнее и дешевле) и трёхчиповыми (точнее цветопередача). Выбор ведут под задачи и бюджет отделения.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5248,13 +5198,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Отдельные блоки и интегрированные системы</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Отдельный блок управления камерой (Mindray HD3, HyPixel U1) работает со стойкой и источником света, узлы меняются по отдельности. Интегрированные системы MGB ELICA III и Fencer III «4 в 1» объединяют камеру, свет, а также инсуффлятор и ирригатор в одном корпусе. Первый вариант гибче, второй компактнее.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5271,6 +5221,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Модели каталога</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Каталог включает видеоинформационные центры Olympus Visera (Elite, Elite II, 4K UHD), блоки управления камерой Mindray (HD3 Full HD, HyPixel U1 4K), интегрированные системы MGB (ELICA III, Fencer III, камеры ARISTO-V1 и V3) и отечественные камеры НПФ Крыло (КРВ 1001, 1001HD, 1001ОС) и «Элепс» EVK-001. Разрешение — от HD до 4K UHD.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>videoprotsessory_dlya_zhestkoy_endoskopii</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
